--- a/Employee_Reports_wi48/Harsha Shetty Q0603.xlsx
+++ b/Employee_Reports_wi48/Harsha Shetty Q0603.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>15-May-2025</t>
+          <t>13-Jul-2026</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>15-May-2027</t>
+          <t>12-Jul-2028</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>306</v>
+        <v>727</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cool Room (Cargo Trainings)</t>
+          <t>Truck dock 20FT (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-011</t>
+          <t>LSME-CRG-M-020</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1108,20 +1108,20 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2026</t>
+          <t>13-Jul-2026</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2028</t>
+          <t>12-Jul-2028</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>562</v>
+        <v>727</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Climate Control Center (Cargo Trainings)</t>
+          <t>Cool Room (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-014</t>
+          <t>LSME-CRG-M-011</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Diagnosis Of Beckoff Module And Troubleshooting Guide (Cargo Trainings)</t>
+          <t>Climate Control Center (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-012</t>
+          <t>LSME-CRG-M-014</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1206,20 +1206,20 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>19-Oct-2025</t>
+          <t>26-Jan-2026</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>19-Oct-2027</t>
+          <t>26-Jan-2028</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>463</v>
+        <v>559</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1235,28 +1235,40 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Powered roller Decks2 (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
+          <t>Diagnosis Of Beckoff Module And Troubleshooting Guide (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-012</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>21-Feb-2026</t>
+          <t>19-Oct-2025</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>21-Feb-2028</t>
+          <t>19-Oct-2027</t>
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>588</v>
+        <v>460</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1272,40 +1284,28 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Lodige LOTO Procedure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>ELECTRICAL SAFETY</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>LSME-OHS-SOP-021</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
+          <t>Powered roller Decks2 (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>07-Dec-2025</t>
+          <t>21-Feb-2026</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>07-Dec-2026</t>
+          <t>21-Feb-2028</t>
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>147</v>
+        <v>585</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1321,18 +1321,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Equipment Operation Procedure
-(SOP-031) (SOPs)</t>
+          <t>Lodige LOTO Procedure (SOPs)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>CARGO</t>
+          <t>ELECTRICAL SAFETY</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-031</t>
+          <t>LSME-OHS-SOP-021</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1342,20 +1341,20 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>13-Oct-2025</t>
+          <t>07-Dec-2025</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>07-Dec-2026</t>
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1371,7 +1370,8 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
+          <t>Equipment Operation Procedure
+(SOP-031) (SOPs)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-028</t>
+          <t>LSME-CRG-SOP-031</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1400,11 +1400,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>STACKER CRANE AISLE MONTHLY PREVENTIVE MAINTENANCE (SOPs)</t>
+          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-035</t>
+          <t>LSME-CRG-SOP-028</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1469,28 +1469,40 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Endangered by Electricity A safety Training (SOPs)</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
+          <t>STACKER CRANE AISLE MONTHLY PREVENTIVE MAINTENANCE (SOPs)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-035</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>19-Nov-2025</t>
+          <t>13-Oct-2025</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>19-Nov-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1506,40 +1518,28 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Incident Escalation Process(LSME-IMS-SOP-021 ) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>IMS</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>LSME-IMS-SOP-021</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
+          <t>Endangered by Electricity A safety Training (SOPs)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>13-Oct-2025</t>
+          <t>19-Nov-2025</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>19-Nov-2026</t>
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Misaligned Pallet-ULD Recovery Procedure (SOPs)</t>
+          <t>Incident Escalation Process(LSME-IMS-SOP-021 ) (SOPs)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>CARGO</t>
+          <t>IMS</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-030</t>
+          <t>LSME-IMS-SOP-021</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1584,11 +1584,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1604,17 +1604,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
+          <t>Misaligned Pallet-ULD Recovery Procedure (SOPs)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>IMS</t>
+          <t>CARGO</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>LSME-IMS-SOP-018</t>
+          <t>LSME-CRG-SOP-030</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1624,20 +1624,20 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>13-Dec-2025</t>
+          <t>13-Oct-2025</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>13-Dec-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>153</v>
+        <v>89</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1653,28 +1653,40 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
+          <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-018</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>16-Dec-2025</t>
+          <t>13-Dec-2025</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>16-Dec-2026</t>
+          <t>13-Dec-2026</t>
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1690,17 +1702,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
+          <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>CARGO</t>
+          <t>IMS</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-041</t>
+          <t>LSME-IMS-SOP-022</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1710,20 +1722,20 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>16-Dec-2025</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>08-Apr-2027</t>
+          <t>16-Dec-2026</t>
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>269</v>
+        <v>153</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1739,97 +1751,97 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-041</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>08-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>08-Apr-2027</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
           <t>Stacker Crane Aisle Annual Maintenance And Megger Test Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-003</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>19-Dec-2025</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>19-Dec-2026</t>
         </is>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>159</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Replacement of Stacker Crane Driven Wheel (SOPs)</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-009</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>23-Jul-2025</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>23-Jul-2026</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr"/>
+      <c r="H29" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1837,97 +1849,97 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
+          <t>Replacement of Stacker Crane Driven Wheel (SOPs)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-009</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>23-Jul-2025</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>23-Jul-2026</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
           <t>Replacement of Stacker Crane Fork Flyer Chain (SOPs)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-010</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>23-Jul-2025</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>23-Jul-2026</t>
         </is>
       </c>
-      <c r="H30" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="H31" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Matar LOTO Procedure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>MATAR</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>FM-DE-24-SOP-SA-013</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>19-Nov-2025</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>19-Nov-2026</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -1935,28 +1947,40 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>20FT Floor Scale Weight Discrepancy Troubleshooting Guide (SOPs)</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
+          <t>Matar LOTO Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>MATAR</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>FM-DE-24-SOP-SA-013</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>25-Jan-2026</t>
+          <t>19-Nov-2025</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>25-Jan-2027</t>
+          <t>19-Nov-2026</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>196</v>
+        <v>126</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1972,40 +1996,28 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Chiller Room Door Teaching Procedure For Door Control Panel Ts 981 (SOPs)</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-025</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
+          <t>20FT Floor Scale Weight Discrepancy Troubleshooting Guide (SOPs)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>29-Jan-2026</t>
+          <t>25-Jan-2026</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>29-Jan-2027</t>
+          <t>25-Jan-2027</t>
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2021,36 +2033,85 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
+          <t>Chiller Room Door Teaching Procedure For Door Control Panel Ts 981 (SOPs)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-025</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>29-Jan-2026</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>29-Jan-2027</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>01-Jul-2025</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>01-Jul-2027</t>
         </is>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>353</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2521,11 +2582,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="57" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -2593,7 +2654,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7814</v>
+        <v>7811</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2613,16 +2674,16 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>18-Mar-2048</t>
+          <t>06-Jun-2048</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7919</v>
+        <v>7996</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2630,6 +2691,151 @@
         </is>
       </c>
       <c r="G4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Motor Clutch Cleaning And Lubrication- Power Roller Deck</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>06-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7996</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Chain Cleaning And Lubrication- Power Roller Deck</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>06-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>7996</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Chain Elongation -H9TV</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>06-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>7996</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Chain Elongation -Truck Dock</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>06-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>7996</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Chain Cleaning And Lubrication-Truck Dock</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>06-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>7996</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2645,11 +2851,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -2717,7 +2923,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2746,7 +2952,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2775,7 +2981,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2790,21 +2996,21 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>uld hoist</t>
+          <t>ews 20ft</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>04-Jul-2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>26-Apr-2048</t>
+          <t>29-May-2048</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7958</v>
+        <v>7988</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2819,21 +3025,21 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>tilting deck</t>
+          <t>ews 10 ft</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>04-Jul-2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>26-Apr-2048</t>
+          <t>29-May-2048</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7958</v>
+        <v>7988</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2848,21 +3054,21 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>uldtv 20ft</t>
+          <t>uld hoist</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>27-Apr-2048</t>
+          <t>26-Apr-2048</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7959</v>
+        <v>7955</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2877,21 +3083,21 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>uldtv 15ft</t>
+          <t>truckdock 15ft</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>04-Jul-2026</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>26-Apr-2048</t>
+          <t>29-May-2048</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7958</v>
+        <v>7988</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2906,21 +3112,21 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>bbtv 20ft</t>
+          <t>truckdock  20ft</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>04-Jul-2026</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>27-Apr-2048</t>
+          <t>29-May-2048</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7959</v>
+        <v>7988</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2935,21 +3141,21 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>bbtv 15ft</t>
+          <t>turntable</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>02-Jun-2026</t>
+          <t>05-Jul-2026</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>27-Apr-2048</t>
+          <t>30-May-2048</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7959</v>
+        <v>7989</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2964,21 +3170,21 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>cs placing deck</t>
+          <t>tilting deck</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>14-Jun-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>09-May-2048</t>
+          <t>26-Apr-2048</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7971</v>
+        <v>7955</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2993,28 +3199,318 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>uldtv 20ft</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>02-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>27-Apr-2048</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>7956</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>uldtv 15ft</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2048</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>7955</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>bbtv 20ft</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>02-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>27-Apr-2048</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>7956</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>bbtv 15ft</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>02-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>27-Apr-2048</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>7956</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>fmc deck</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>03-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>28-May-2048</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>7987</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>powered roller deckmatarsop</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>04-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>29-May-2048</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>7988</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>non powered roller deckmatarsop</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>04-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>29-May-2048</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>7988</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>cs placing deck</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>14-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>09-May-2048</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>7968</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>cs input and output conveyor</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>14-Jun-2026</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>09-May-2048</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>7971</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n"/>
+      <c r="E21" s="3" t="n">
+        <v>7968</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>ball deck</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>03-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>28-May-2048</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>7987</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>floor scale</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>04-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>29-May-2048</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>7988</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
